--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
@@ -257,13 +257,13 @@
         <v>1418</v>
       </c>
       <c r="K2" s="0">
-        <v>4877</v>
+        <v>4876.6899999999996</v>
       </c>
       <c r="L2" s="0">
         <v>28.449999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="3">
@@ -298,13 +298,13 @@
         <v>904</v>
       </c>
       <c r="K3" s="0">
-        <v>5354</v>
+        <v>5353.8500000000004</v>
       </c>
       <c r="L3" s="0">
         <v>30.399999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -339,13 +339,13 @@
         <v>1154</v>
       </c>
       <c r="K4" s="0">
-        <v>7024</v>
+        <v>7023.9799999999996</v>
       </c>
       <c r="L4" s="0">
         <v>37.869999999999997</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="5">
@@ -380,13 +380,13 @@
         <v>941</v>
       </c>
       <c r="K5" s="0">
-        <v>4542</v>
+        <v>4541.7200000000003</v>
       </c>
       <c r="L5" s="0">
         <v>33.659999999999997</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -421,13 +421,13 @@
         <v>1201</v>
       </c>
       <c r="K6" s="0">
-        <v>6593</v>
+        <v>6592.54</v>
       </c>
       <c r="L6" s="0">
         <v>34.789999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="7">
@@ -462,13 +462,13 @@
         <v>893</v>
       </c>
       <c r="K7" s="0">
-        <v>4846</v>
+        <v>4846.0900000000001</v>
       </c>
       <c r="L7" s="0">
         <v>23.57</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>1088</v>
       </c>
       <c r="K8" s="0">
-        <v>8154</v>
+        <v>8153.6999999999998</v>
       </c>
       <c r="L8" s="0">
         <v>36.299999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="9">
@@ -544,13 +544,13 @@
         <v>1282</v>
       </c>
       <c r="K9" s="0">
-        <v>5445</v>
+        <v>5445.4200000000001</v>
       </c>
       <c r="L9" s="0">
         <v>34.25</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         <v>763</v>
       </c>
       <c r="K10" s="0">
-        <v>4873</v>
+        <v>4872.7200000000003</v>
       </c>
       <c r="L10" s="0">
         <v>30.359999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="11">
@@ -626,13 +626,13 @@
         <v>973</v>
       </c>
       <c r="K11" s="0">
-        <v>4830</v>
+        <v>4830.3800000000001</v>
       </c>
       <c r="L11" s="0">
         <v>25.390000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="12">
@@ -667,13 +667,13 @@
         <v>1110</v>
       </c>
       <c r="K12" s="0">
-        <v>5299</v>
+        <v>5298.6599999999999</v>
       </c>
       <c r="L12" s="0">
         <v>28.699999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="13">
@@ -708,13 +708,13 @@
         <v>1504</v>
       </c>
       <c r="K13" s="0">
-        <v>7047</v>
+        <v>7047.4399999999996</v>
       </c>
       <c r="L13" s="0">
         <v>36.079999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="14">
@@ -749,13 +749,13 @@
         <v>388</v>
       </c>
       <c r="K14" s="0">
-        <v>1658</v>
+        <v>1657.78</v>
       </c>
       <c r="L14" s="0">
         <v>33.130000000000003</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -790,7 +790,7 @@
         <v>453</v>
       </c>
       <c r="K15" s="0">
-        <v>1819</v>
+        <v>1819.4300000000001</v>
       </c>
       <c r="L15" s="0">
         <v>24.300000000000001</v>
@@ -831,13 +831,13 @@
         <v>530</v>
       </c>
       <c r="K16" s="0">
-        <v>1997</v>
+        <v>1997.0599999999999</v>
       </c>
       <c r="L16" s="0">
         <v>27.170000000000002</v>
       </c>
       <c r="M16" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="17">
@@ -872,13 +872,13 @@
         <v>339</v>
       </c>
       <c r="K17" s="0">
-        <v>2513</v>
+        <v>2513.4099999999999</v>
       </c>
       <c r="L17" s="0">
         <v>50.270000000000003</v>
       </c>
       <c r="M17" s="0">
-        <v>0.23000000000000001</v>
+        <v>0.22800000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -913,13 +913,13 @@
         <v>484</v>
       </c>
       <c r="K18" s="0">
-        <v>1835</v>
+        <v>1834.6500000000001</v>
       </c>
       <c r="L18" s="0">
         <v>24.140000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="19">
@@ -954,13 +954,13 @@
         <v>542</v>
       </c>
       <c r="K19" s="0">
-        <v>1799</v>
+        <v>1799.47</v>
       </c>
       <c r="L19" s="0">
         <v>24.109999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="20">
@@ -995,13 +995,13 @@
         <v>291</v>
       </c>
       <c r="K20" s="0">
-        <v>2234</v>
+        <v>2234.2199999999998</v>
       </c>
       <c r="L20" s="0">
         <v>44.68</v>
       </c>
       <c r="M20" s="0">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="21">
@@ -1036,13 +1036,13 @@
         <v>431</v>
       </c>
       <c r="K21" s="0">
-        <v>2445</v>
+        <v>2445.25</v>
       </c>
       <c r="L21" s="0">
         <v>33.899999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.13</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1077,13 +1077,13 @@
         <v>488</v>
       </c>
       <c r="K22" s="0">
-        <v>1660</v>
+        <v>1659.51</v>
       </c>
       <c r="L22" s="0">
         <v>22.16</v>
       </c>
       <c r="M22" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="23">
@@ -1118,13 +1118,13 @@
         <v>460</v>
       </c>
       <c r="K23" s="0">
-        <v>1651</v>
+        <v>1650.6199999999999</v>
       </c>
       <c r="L23" s="0">
         <v>23.77</v>
       </c>
       <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="24">
@@ -1159,13 +1159,13 @@
         <v>940</v>
       </c>
       <c r="K24" s="0">
-        <v>5393</v>
+        <v>5393.1499999999996</v>
       </c>
       <c r="L24" s="0">
         <v>33.219999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -166,7 +169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +192,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -353,40 +356,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>3871656854</v>
+        <v>1972156630</v>
       </c>
       <c r="C5" s="0">
-        <v>5062690531</v>
+        <v>2677614354</v>
       </c>
       <c r="D5" s="0">
-        <v>394598</v>
+        <v>569705</v>
       </c>
       <c r="E5" s="0">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F5" s="0">
-        <v>39825</v>
+        <v>19701</v>
       </c>
       <c r="G5" s="0">
-        <v>3.1000000000000001</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="H5" s="0">
-        <v>8.0700000000000003</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="I5" s="0">
-        <v>76.469999999999999</v>
+        <v>73.650000000000006</v>
       </c>
       <c r="J5" s="0">
-        <v>941</v>
+        <v>788</v>
       </c>
       <c r="K5" s="0">
-        <v>4541.7200000000003</v>
+        <v>4513.8100000000004</v>
       </c>
       <c r="L5" s="0">
-        <v>33.659999999999997</v>
+        <v>26.239999999999998</v>
       </c>
       <c r="M5" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +397,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>231747918812</v>
+        <v>3871656854</v>
       </c>
       <c r="C6" s="0">
-        <v>270767789817</v>
+        <v>5062690531</v>
       </c>
       <c r="D6" s="0">
-        <v>776462</v>
+        <v>394598</v>
       </c>
       <c r="E6" s="0">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="F6" s="0">
-        <v>1153628</v>
+        <v>39825</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3100000000000001</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>10.07</v>
+        <v>8.0700000000000003</v>
       </c>
       <c r="I6" s="0">
-        <v>85.590000000000003</v>
+        <v>76.469999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>1201</v>
+        <v>941</v>
       </c>
       <c r="K6" s="0">
-        <v>6592.54</v>
+        <v>4541.7200000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>34.789999999999999</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M6" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +438,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>30594586277</v>
+        <v>231747918812</v>
       </c>
       <c r="C7" s="0">
-        <v>39823848016</v>
+        <v>270767789817</v>
       </c>
       <c r="D7" s="0">
-        <v>743398</v>
+        <v>776462</v>
       </c>
       <c r="E7" s="0">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="F7" s="0">
-        <v>216369</v>
+        <v>1153628</v>
       </c>
       <c r="G7" s="0">
-        <v>4.04</v>
+        <v>3.3100000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>10.35</v>
+        <v>10.07</v>
       </c>
       <c r="I7" s="0">
-        <v>76.819999999999993</v>
+        <v>85.590000000000003</v>
       </c>
       <c r="J7" s="0">
-        <v>893</v>
+        <v>1201</v>
       </c>
       <c r="K7" s="0">
-        <v>4846.0900000000001</v>
+        <v>6592.54</v>
       </c>
       <c r="L7" s="0">
-        <v>23.57</v>
+        <v>34.789999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +479,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>17832554875</v>
+        <v>30594586277</v>
       </c>
       <c r="C8" s="0">
-        <v>21264833726</v>
+        <v>39823848016</v>
       </c>
       <c r="D8" s="0">
-        <v>919362</v>
+        <v>743398</v>
       </c>
       <c r="E8" s="0">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="F8" s="0">
-        <v>82207</v>
+        <v>216369</v>
       </c>
       <c r="G8" s="0">
-        <v>3.5499999999999998</v>
+        <v>4.04</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4100000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="I8" s="0">
-        <v>83.859999999999999</v>
+        <v>76.819999999999993</v>
       </c>
       <c r="J8" s="0">
-        <v>1088</v>
+        <v>893</v>
       </c>
       <c r="K8" s="0">
-        <v>8153.6999999999998</v>
+        <v>4846.0900000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>36.299999999999997</v>
+        <v>23.57</v>
       </c>
       <c r="M8" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +520,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>54990949428</v>
+        <v>17832554875</v>
       </c>
       <c r="C9" s="0">
-        <v>66122319792</v>
+        <v>21264833726</v>
       </c>
       <c r="D9" s="0">
-        <v>633538</v>
+        <v>919362</v>
       </c>
       <c r="E9" s="0">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F9" s="0">
-        <v>321396</v>
+        <v>82207</v>
       </c>
       <c r="G9" s="0">
-        <v>3.0800000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>10.15</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I9" s="0">
-        <v>83.170000000000002</v>
+        <v>83.859999999999999</v>
       </c>
       <c r="J9" s="0">
-        <v>1282</v>
+        <v>1088</v>
       </c>
       <c r="K9" s="0">
-        <v>5445.4200000000001</v>
+        <v>8153.6999999999998</v>
       </c>
       <c r="L9" s="0">
-        <v>34.25</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="M9" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +561,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>142538698065</v>
+        <v>54990949428</v>
       </c>
       <c r="C10" s="0">
-        <v>177277723134</v>
+        <v>66122319792</v>
       </c>
       <c r="D10" s="0">
-        <v>594952</v>
+        <v>633538</v>
       </c>
       <c r="E10" s="0">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F10" s="0">
-        <v>1444037</v>
+        <v>321396</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8499999999999996</v>
+        <v>3.0800000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>10.109999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="I10" s="0">
-        <v>80.400000000000006</v>
+        <v>83.170000000000002</v>
       </c>
       <c r="J10" s="0">
-        <v>763</v>
+        <v>1282</v>
       </c>
       <c r="K10" s="0">
-        <v>4872.7200000000003</v>
+        <v>5445.4200000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>30.359999999999999</v>
+        <v>34.25</v>
       </c>
       <c r="M10" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +602,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>43673945621</v>
+        <v>142538698065</v>
       </c>
       <c r="C11" s="0">
-        <v>53021457459</v>
+        <v>177277723134</v>
       </c>
       <c r="D11" s="0">
-        <v>689755</v>
+        <v>594952</v>
       </c>
       <c r="E11" s="0">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="F11" s="0">
-        <v>286215</v>
+        <v>1444037</v>
       </c>
       <c r="G11" s="0">
-        <v>3.7200000000000002</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="H11" s="0">
-        <v>9.7799999999999994</v>
+        <v>10.109999999999999</v>
       </c>
       <c r="I11" s="0">
-        <v>82.370000000000005</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="J11" s="0">
-        <v>973</v>
+        <v>763</v>
       </c>
       <c r="K11" s="0">
-        <v>4830.3800000000001</v>
+        <v>4872.7200000000003</v>
       </c>
       <c r="L11" s="0">
-        <v>25.390000000000001</v>
+        <v>30.359999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +643,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>6275985654</v>
+        <v>43673945621</v>
       </c>
       <c r="C12" s="0">
-        <v>7923538076</v>
+        <v>53021457459</v>
       </c>
       <c r="D12" s="0">
-        <v>388599</v>
+        <v>689755</v>
       </c>
       <c r="E12" s="0">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F12" s="0">
-        <v>38679</v>
+        <v>286215</v>
       </c>
       <c r="G12" s="0">
-        <v>1.8999999999999999</v>
+        <v>3.7200000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>5.5300000000000002</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="I12" s="0">
-        <v>79.209999999999994</v>
+        <v>82.370000000000005</v>
       </c>
       <c r="J12" s="0">
-        <v>1110</v>
+        <v>973</v>
       </c>
       <c r="K12" s="0">
-        <v>5298.6599999999999</v>
+        <v>4830.3800000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>28.699999999999999</v>
+        <v>25.390000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +684,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>242852397251</v>
+        <v>6275985654</v>
       </c>
       <c r="C13" s="0">
-        <v>292499643926</v>
+        <v>7923538076</v>
       </c>
       <c r="D13" s="0">
-        <v>828118</v>
+        <v>388599</v>
       </c>
       <c r="E13" s="0">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F13" s="0">
-        <v>963233</v>
+        <v>38679</v>
       </c>
       <c r="G13" s="0">
-        <v>2.73</v>
+        <v>1.8999999999999999</v>
       </c>
       <c r="H13" s="0">
-        <v>10</v>
+        <v>5.5300000000000002</v>
       </c>
       <c r="I13" s="0">
-        <v>83.030000000000001</v>
+        <v>79.209999999999994</v>
       </c>
       <c r="J13" s="0">
-        <v>1504</v>
+        <v>1110</v>
       </c>
       <c r="K13" s="0">
-        <v>7047.4399999999996</v>
+        <v>5298.6599999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>36.079999999999998</v>
+        <v>28.699999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +725,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1246661535</v>
+        <v>242852397251</v>
       </c>
       <c r="C14" s="0">
-        <v>1453702101</v>
+        <v>292499643926</v>
       </c>
       <c r="D14" s="0">
-        <v>71540</v>
+        <v>828118</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="F14" s="0">
-        <v>74849</v>
+        <v>963233</v>
       </c>
       <c r="G14" s="0">
-        <v>3.6800000000000002</v>
+        <v>2.73</v>
       </c>
       <c r="H14" s="0">
-        <v>5.6799999999999997</v>
+        <v>10</v>
       </c>
       <c r="I14" s="0">
-        <v>85.760000000000005</v>
+        <v>83.030000000000001</v>
       </c>
       <c r="J14" s="0">
-        <v>388</v>
+        <v>1504</v>
       </c>
       <c r="K14" s="0">
-        <v>1657.78</v>
+        <v>7047.4399999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>33.130000000000003</v>
+        <v>36.079999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13200000000000001</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +766,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5889366892</v>
+        <v>1246661535</v>
       </c>
       <c r="C15" s="0">
-        <v>7206600275</v>
+        <v>1453702101</v>
       </c>
       <c r="D15" s="0">
-        <v>146386</v>
+        <v>71540</v>
       </c>
       <c r="E15" s="0">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F15" s="0">
-        <v>212404</v>
+        <v>74849</v>
       </c>
       <c r="G15" s="0">
-        <v>4.3099999999999996</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>7.2300000000000004</v>
+        <v>5.6799999999999997</v>
       </c>
       <c r="I15" s="0">
-        <v>81.719999999999999</v>
+        <v>85.760000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>453</v>
+        <v>388</v>
       </c>
       <c r="K15" s="0">
-        <v>1819.4300000000001</v>
+        <v>1657.78</v>
       </c>
       <c r="L15" s="0">
-        <v>24.300000000000001</v>
+        <v>33.130000000000003</v>
       </c>
       <c r="M15" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +807,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>9731833342</v>
+        <v>5889366892</v>
       </c>
       <c r="C16" s="0">
-        <v>11747610712</v>
+        <v>7206600275</v>
       </c>
       <c r="D16" s="0">
-        <v>68909</v>
+        <v>146386</v>
       </c>
       <c r="E16" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" s="0">
-        <v>300792</v>
+        <v>212404</v>
       </c>
       <c r="G16" s="0">
-        <v>1.76</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="H16" s="0">
-        <v>3.1699999999999999</v>
+        <v>7.2300000000000004</v>
       </c>
       <c r="I16" s="0">
-        <v>82.840000000000003</v>
+        <v>81.719999999999999</v>
       </c>
       <c r="J16" s="0">
-        <v>530</v>
+        <v>453</v>
       </c>
       <c r="K16" s="0">
-        <v>1997.0599999999999</v>
+        <v>1819.4300000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>27.170000000000002</v>
+        <v>24.300000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +848,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>805602122</v>
+        <v>9731833342</v>
       </c>
       <c r="C17" s="0">
-        <v>951096350</v>
+        <v>11747610712</v>
       </c>
       <c r="D17" s="0">
-        <v>39596</v>
+        <v>68909</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F17" s="0">
-        <v>56189</v>
+        <v>300792</v>
       </c>
       <c r="G17" s="0">
-        <v>2.3399999999999999</v>
+        <v>1.76</v>
       </c>
       <c r="H17" s="0">
-        <v>3.6000000000000001</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>84.700000000000003</v>
+        <v>82.840000000000003</v>
       </c>
       <c r="J17" s="0">
-        <v>339</v>
+        <v>530</v>
       </c>
       <c r="K17" s="0">
-        <v>2513.4099999999999</v>
+        <v>1997.0599999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>50.270000000000003</v>
+        <v>27.170000000000002</v>
       </c>
       <c r="M17" s="0">
-        <v>0.22800000000000001</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +889,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>2669587603</v>
+        <v>805602122</v>
       </c>
       <c r="C18" s="0">
-        <v>3195288064</v>
+        <v>951096350</v>
       </c>
       <c r="D18" s="0">
-        <v>202875</v>
+        <v>39596</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
-        <v>86908</v>
+        <v>56189</v>
       </c>
       <c r="G18" s="0">
-        <v>5.5199999999999996</v>
+        <v>2.3399999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>8.9000000000000004</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="I18" s="0">
-        <v>83.549999999999997</v>
+        <v>84.700000000000003</v>
       </c>
       <c r="J18" s="0">
-        <v>484</v>
+        <v>339</v>
       </c>
       <c r="K18" s="0">
-        <v>1834.6500000000001</v>
+        <v>2513.4099999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>24.140000000000001</v>
+        <v>50.270000000000003</v>
       </c>
       <c r="M18" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.22800000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -927,37 +930,37 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3124636862</v>
+        <v>2669587603</v>
       </c>
       <c r="C19" s="0">
-        <v>3751789548</v>
+        <v>3195288064</v>
       </c>
       <c r="D19" s="0">
-        <v>177726</v>
+        <v>202875</v>
       </c>
       <c r="E19" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>92761</v>
+        <v>86908</v>
       </c>
       <c r="G19" s="0">
-        <v>4.3899999999999997</v>
+        <v>5.5199999999999996</v>
       </c>
       <c r="H19" s="0">
-        <v>7.9699999999999998</v>
+        <v>8.9000000000000004</v>
       </c>
       <c r="I19" s="0">
-        <v>83.280000000000001</v>
+        <v>83.549999999999997</v>
       </c>
       <c r="J19" s="0">
-        <v>542</v>
+        <v>484</v>
       </c>
       <c r="K19" s="0">
-        <v>1799.47</v>
+        <v>1834.6500000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>24.109999999999999</v>
+        <v>24.140000000000001</v>
       </c>
       <c r="M19" s="0">
         <v>0.081000000000000003</v>
@@ -968,40 +971,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1470731990</v>
+        <v>3124636862</v>
       </c>
       <c r="C20" s="0">
-        <v>1723820015</v>
+        <v>3751789548</v>
       </c>
       <c r="D20" s="0">
-        <v>76888</v>
+        <v>177306</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F20" s="0">
-        <v>118539</v>
+        <v>92761</v>
       </c>
       <c r="G20" s="0">
-        <v>5.29</v>
+        <v>4.3799999999999999</v>
       </c>
       <c r="H20" s="0">
-        <v>7.6500000000000004</v>
+        <v>7.96</v>
       </c>
       <c r="I20" s="0">
-        <v>85.319999999999993</v>
+        <v>83.280000000000001</v>
       </c>
       <c r="J20" s="0">
-        <v>291</v>
+        <v>542</v>
       </c>
       <c r="K20" s="0">
-        <v>2234.2199999999998</v>
+        <v>1817.23</v>
       </c>
       <c r="L20" s="0">
-        <v>44.68</v>
+        <v>24.350000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.222</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1012,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5949132416</v>
+        <v>1470731990</v>
       </c>
       <c r="C21" s="0">
-        <v>7190106582</v>
+        <v>1723820015</v>
       </c>
       <c r="D21" s="0">
-        <v>133002</v>
+        <v>76888</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" s="0">
-        <v>231384</v>
+        <v>118539</v>
       </c>
       <c r="G21" s="0">
-        <v>4.2800000000000002</v>
+        <v>5.29</v>
       </c>
       <c r="H21" s="0">
-        <v>7.1799999999999997</v>
+        <v>7.6500000000000004</v>
       </c>
       <c r="I21" s="0">
-        <v>82.739999999999995</v>
+        <v>85.319999999999993</v>
       </c>
       <c r="J21" s="0">
-        <v>431</v>
+        <v>291</v>
       </c>
       <c r="K21" s="0">
-        <v>2445.25</v>
+        <v>2234.2199999999998</v>
       </c>
       <c r="L21" s="0">
-        <v>33.899999999999999</v>
+        <v>44.68</v>
       </c>
       <c r="M21" s="0">
-        <v>0.13200000000000001</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1053,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>9421151987</v>
+        <v>5949132416</v>
       </c>
       <c r="C22" s="0">
-        <v>11861309538</v>
+        <v>7190106582</v>
       </c>
       <c r="D22" s="0">
-        <v>136462</v>
+        <v>133002</v>
       </c>
       <c r="E22" s="0">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0">
-        <v>324345</v>
+        <v>231384</v>
       </c>
       <c r="G22" s="0">
-        <v>3.73</v>
+        <v>4.2800000000000002</v>
       </c>
       <c r="H22" s="0">
-        <v>6.8099999999999996</v>
+        <v>7.1799999999999997</v>
       </c>
       <c r="I22" s="0">
-        <v>79.430000000000007</v>
+        <v>82.739999999999995</v>
       </c>
       <c r="J22" s="0">
-        <v>488</v>
+        <v>431</v>
       </c>
       <c r="K22" s="0">
-        <v>1659.51</v>
+        <v>2445.25</v>
       </c>
       <c r="L22" s="0">
-        <v>22.16</v>
+        <v>33.899999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1094,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>20207839857</v>
+        <v>9421151987</v>
       </c>
       <c r="C23" s="0">
-        <v>24855479140</v>
+        <v>11861309538</v>
       </c>
       <c r="D23" s="0">
-        <v>122883</v>
+        <v>136462</v>
       </c>
       <c r="E23" s="0">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F23" s="0">
-        <v>771108</v>
+        <v>324345</v>
       </c>
       <c r="G23" s="0">
-        <v>3.8100000000000001</v>
+        <v>3.73</v>
       </c>
       <c r="H23" s="0">
-        <v>6.4299999999999997</v>
+        <v>6.8099999999999996</v>
       </c>
       <c r="I23" s="0">
-        <v>81.299999999999997</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="J23" s="0">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="K23" s="0">
-        <v>1650.6199999999999</v>
+        <v>1659.51</v>
       </c>
       <c r="L23" s="0">
-        <v>23.77</v>
+        <v>22.16</v>
       </c>
       <c r="M23" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="24">
@@ -1132,39 +1135,80 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>1127338610263</v>
+        <v>20207839857</v>
       </c>
       <c r="C24" s="0">
-        <v>1351749889979</v>
+        <v>24855479140</v>
       </c>
       <c r="D24" s="0">
-        <v>553519</v>
+        <v>122883</v>
       </c>
       <c r="E24" s="0">
+        <v>69</v>
+      </c>
+      <c r="F24" s="0">
+        <v>771108</v>
+      </c>
+      <c r="G24" s="0">
+        <v>3.8100000000000001</v>
+      </c>
+      <c r="H24" s="0">
+        <v>6.4299999999999997</v>
+      </c>
+      <c r="I24" s="0">
+        <v>81.299999999999997</v>
+      </c>
+      <c r="J24" s="0">
+        <v>460</v>
+      </c>
+      <c r="K24" s="0">
+        <v>1650.6199999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>23.77</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.085999999999999993</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1129310766893</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1354427504333</v>
+      </c>
+      <c r="D25" s="0">
+        <v>553539</v>
+      </c>
+      <c r="E25" s="0">
         <v>143</v>
       </c>
-      <c r="F24" s="0">
-        <v>8384987</v>
-      </c>
-      <c r="G24" s="0">
+      <c r="F25" s="0">
+        <v>8404688</v>
+      </c>
+      <c r="G25" s="0">
         <v>3.4300000000000002</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H25" s="0">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I24" s="0">
-        <v>83.400000000000006</v>
-      </c>
-      <c r="J24" s="0">
+      <c r="I25" s="0">
+        <v>83.379999999999995</v>
+      </c>
+      <c r="J25" s="0">
         <v>940</v>
       </c>
-      <c r="K24" s="0">
-        <v>5393.1499999999996</v>
-      </c>
-      <c r="L24" s="0">
-        <v>33.219999999999999</v>
-      </c>
-      <c r="M24" s="0">
+      <c r="K25" s="0">
+        <v>5391.4099999999999</v>
+      </c>
+      <c r="L25" s="0">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M25" s="0">
         <v>0.085999999999999993</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Airline_Cumulative_Statistics_2024.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>697723350830</v>
+      </c>
+      <c r="C25" s="0">
+        <v>824810653608</v>
+      </c>
+      <c r="D25" s="0">
+        <v>781418</v>
+      </c>
+      <c r="E25" s="0">
+        <v>174</v>
+      </c>
+      <c r="F25" s="0">
+        <v>3307852</v>
+      </c>
+      <c r="G25" s="0">
+        <v>3.1299999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>10.06</v>
+      </c>
+      <c r="I25" s="0">
+        <v>84.590000000000003</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1272</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6889.1099999999997</v>
+      </c>
+      <c r="L25" s="0">
+        <v>36.240000000000002</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.088999999999999996</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>272917336483</v>
+      </c>
+      <c r="C26" s="0">
+        <v>333605518247</v>
+      </c>
+      <c r="D26" s="0">
+        <v>637223</v>
+      </c>
+      <c r="E26" s="0">
+        <v>160</v>
+      </c>
+      <c r="F26" s="0">
+        <v>2149642</v>
+      </c>
+      <c r="G26" s="0">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H26" s="0">
+        <v>10.16</v>
+      </c>
+      <c r="I26" s="0">
+        <v>81.810000000000002</v>
+      </c>
+      <c r="J26" s="0">
+        <v>936</v>
+      </c>
+      <c r="K26" s="0">
+        <v>5115.2299999999996</v>
+      </c>
+      <c r="L26" s="0">
+        <v>31.140000000000001</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>98153534974</v>
+      </c>
+      <c r="C27" s="0">
+        <v>122074530153</v>
+      </c>
+      <c r="D27" s="0">
+        <v>606853</v>
+      </c>
+      <c r="E27" s="0">
+        <v>191</v>
+      </c>
+      <c r="F27" s="0">
+        <v>677915</v>
+      </c>
+      <c r="G27" s="0">
+        <v>3.3700000000000001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>8.6799999999999997</v>
+      </c>
+      <c r="I27" s="0">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="J27" s="0">
+        <v>938</v>
+      </c>
+      <c r="K27" s="0">
+        <v>4941.5799999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>25.739999999999998</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>60516544606</v>
+      </c>
+      <c r="C28" s="0">
+        <v>73936802325</v>
+      </c>
+      <c r="D28" s="0">
+        <v>110911</v>
+      </c>
+      <c r="E28" s="0">
+        <v>70</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2269279</v>
+      </c>
+      <c r="G28" s="0">
+        <v>3.3999999999999999</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.79</v>
+      </c>
+      <c r="I28" s="0">
+        <v>81.849999999999994</v>
+      </c>
+      <c r="J28" s="0">
+        <v>460</v>
+      </c>
+      <c r="K28" s="0">
+        <v>1855.3900000000001</v>
+      </c>
+      <c r="L28" s="0">
+        <v>26.43</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.097000000000000003</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>1129310766893</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>1354427504333</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>553539</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>143</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>8404688</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>3.4300000000000002</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>83.379999999999995</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>940</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>5391.4099999999999</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>33.200000000000003</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.085999999999999993</v>
       </c>
     </row>
